--- a/SGC-CKN/Excel/53071946-a9ee-4b72-989b-874a5f861eba_Thanh_Hoá_P7-20_D800_08-04-2026.xlsx
+++ b/SGC-CKN/Excel/53071946-a9ee-4b72-989b-874a5f861eba_Thanh_Hoá_P7-20_D800_08-04-2026.xlsx
@@ -98,11 +98,11 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">11:00
+    <t xml:space="preserve">05:00
 08/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">11:32
+    <t xml:space="preserve">05:32
 08/04/2026</t>
   </si>
   <si>
@@ -115,11 +115,11 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">11:33
+    <t xml:space="preserve">05:33
 08/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">11:45
+    <t xml:space="preserve">05:43
 08/04/2026</t>
   </si>
   <si>
@@ -132,11 +132,11 @@
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">11:49
+    <t xml:space="preserve">05:44
 08/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">13:55
+    <t xml:space="preserve">07:55
 08/04/2026</t>
   </si>
   <si>
@@ -149,7 +149,7 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">07:57
+    <t xml:space="preserve">07:56
 08/04/2026</t>
   </si>
   <si>
@@ -1254,7 +1254,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.1</v>
@@ -1263,10 +1263,10 @@
         <v>0.53</v>
       </c>
       <c r="I11" s="5">
-        <v>6.46</v>
+        <v>7.1</v>
       </c>
       <c r="J11" s="8">
-        <v>12.11</v>
+        <v>13.31</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1295,13 +1295,13 @@
         <v>-9.1</v>
       </c>
       <c r="H12" s="9">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="I12" s="9">
         <v>2</v>
       </c>
       <c r="J12" s="8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>35</v>
@@ -1330,13 +1330,13 @@
         <v>-17.3</v>
       </c>
       <c r="H13" s="12">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="I13" s="12">
         <v>8.2</v>
       </c>
       <c r="J13" s="15">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>40</v>
@@ -1365,13 +1365,13 @@
         <v>-21.6</v>
       </c>
       <c r="H14" s="16">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="I14" s="16">
         <v>4.3</v>
       </c>
       <c r="J14" s="8">
-        <v>5.38</v>
+        <v>5.27</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>35</v>
@@ -1432,16 +1432,16 @@
         <v>-26.6</v>
       </c>
       <c r="G16" s="22">
-        <v>-36.3</v>
+        <v>-36.33</v>
       </c>
       <c r="H16" s="22">
         <v>2.32</v>
       </c>
       <c r="I16" s="22">
-        <v>9.7</v>
+        <v>9.73</v>
       </c>
       <c r="J16" s="15">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>35</v>
@@ -1464,19 +1464,19 @@
         <v>56</v>
       </c>
       <c r="F17" s="25">
-        <v>-36.3</v>
+        <v>-36.33</v>
       </c>
       <c r="G17" s="25">
-        <v>-38.53</v>
+        <v>-38.33</v>
       </c>
       <c r="H17" s="25">
         <v>0.72</v>
       </c>
       <c r="I17" s="25">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="J17" s="15">
-        <v>3.11</v>
+        <v>2.79</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>57</v>
@@ -1499,7 +1499,7 @@
         <v>61</v>
       </c>
       <c r="F18" s="28">
-        <v>-38.53</v>
+        <v>-38.33</v>
       </c>
       <c r="G18" s="28">
         <v>-39.8</v>
@@ -1508,10 +1508,10 @@
         <v>1.02</v>
       </c>
       <c r="I18" s="28">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="J18" s="15">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>62</v>
@@ -1572,16 +1572,16 @@
         <v>-43.8</v>
       </c>
       <c r="G20" s="34">
-        <v>-49.84</v>
+        <v>-44.84</v>
       </c>
       <c r="H20" s="34">
         <v>0.23</v>
       </c>
       <c r="I20" s="34">
-        <v>6.04</v>
-      </c>
-      <c r="J20" s="8">
-        <v>25.89</v>
+        <v>1.04</v>
+      </c>
+      <c r="J20" s="15">
+        <v>4.46</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>71</v>
@@ -1736,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.1</v>
@@ -1745,10 +1745,10 @@
         <v>0.53</v>
       </c>
       <c r="H2" s="5">
-        <v>6.46</v>
+        <v>7.1</v>
       </c>
       <c r="I2" s="8">
-        <v>12.11</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1771,13 +1771,13 @@
         <v>-9.1</v>
       </c>
       <c r="G3" s="9">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="H3" s="9">
         <v>2</v>
       </c>
       <c r="I3" s="8">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1800,13 +1800,13 @@
         <v>-17.3</v>
       </c>
       <c r="G4" s="12">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="H4" s="12">
         <v>8.2</v>
       </c>
       <c r="I4" s="15">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1829,13 +1829,13 @@
         <v>-21.6</v>
       </c>
       <c r="G5" s="16">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H5" s="16">
         <v>4.3</v>
       </c>
       <c r="I5" s="8">
-        <v>5.38</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1884,16 +1884,16 @@
         <v>-26.6</v>
       </c>
       <c r="F7" s="22">
-        <v>-36.3</v>
+        <v>-36.33</v>
       </c>
       <c r="G7" s="22">
         <v>2.32</v>
       </c>
       <c r="H7" s="22">
-        <v>9.7</v>
+        <v>9.73</v>
       </c>
       <c r="I7" s="15">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1910,19 +1910,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-36.3</v>
+        <v>-36.33</v>
       </c>
       <c r="F8" s="25">
-        <v>-38.53</v>
+        <v>-38.33</v>
       </c>
       <c r="G8" s="25">
         <v>0.72</v>
       </c>
       <c r="H8" s="25">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="I8" s="15">
-        <v>3.11</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1939,7 +1939,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-38.53</v>
+        <v>-38.33</v>
       </c>
       <c r="F9" s="28">
         <v>-39.8</v>
@@ -1948,10 +1948,10 @@
         <v>1.02</v>
       </c>
       <c r="H9" s="28">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="I9" s="15">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2000,16 +2000,16 @@
         <v>-43.8</v>
       </c>
       <c r="F11" s="34">
-        <v>-49.84</v>
+        <v>-44.84</v>
       </c>
       <c r="G11" s="34">
         <v>0.23</v>
       </c>
       <c r="H11" s="34">
-        <v>6.04</v>
-      </c>
-      <c r="I11" s="8">
-        <v>25.89</v>
+        <v>1.04</v>
+      </c>
+      <c r="I11" s="15">
+        <v>4.46</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2026,19 +2026,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
-        <v>-49.84</v>
+        <v>-44.84</v>
       </c>
       <c r="G12" s="39">
-        <v>10.02</v>
+        <v>10.08</v>
       </c>
       <c r="H12" s="39">
-        <v>49.2</v>
+        <v>44.84</v>
       </c>
       <c r="I12" s="39">
-        <v>4.91</v>
+        <v>4.45</v>
       </c>
     </row>
   </sheetData>
